--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1042,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1159,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,685 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:33</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1108,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,17 +1169,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1185,13 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1363,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1474,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1585,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1696,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1774,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1807,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1831,17 +1883,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1851,7 +1903,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1861,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1961,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1976,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2076,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2086,12 +2138,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2263,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2307,13 +2359,937 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1941,32 +1941,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1974,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,17 +2002,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2018,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2204,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2315,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2369,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2545,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2890,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3005,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3120,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3164,12 +3168,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3182,22 +3186,22 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3230,12 +3234,12 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3249,45 +3253,156 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>09:18</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="AA25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
+      <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
         </is>
       </c>
-      <c r="AC24" s="2" t="inlineStr">
+      <c r="AC25" s="2" t="inlineStr">
         <is>
           <t>8/11</t>
         </is>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1951,24 +1951,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2060,32 +2060,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,17 +2121,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2137,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2179,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2208,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2232,17 +2240,17 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2252,13 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2286,32 +2298,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2319,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2343,37 +2359,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2401,32 +2417,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2434,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2458,37 +2478,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2516,32 +2536,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2549,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2573,37 +2597,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2631,32 +2655,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2664,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2688,17 +2716,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2708,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2746,32 +2774,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2779,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2803,37 +2835,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,7 +2965,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2948,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3048,7 +3080,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3063,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3173,12 +3205,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3283,13 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3394,17 +3430,707 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr">
-        <is>
-          <t>8/11</t>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2893,32 +2893,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,17 +2954,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2970,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3008,32 +3012,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3041,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3065,17 +3073,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3085,12 +3093,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3123,32 +3131,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3156,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3180,17 +3192,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3200,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3238,32 +3250,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3271,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3295,37 +3311,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3369,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3386,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3410,37 +3430,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3555,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3583,32 +3603,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3616,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3640,37 +3664,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3785,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3909,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3900,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4005,12 +4029,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4076,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4120,17 +4144,592 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>70.0</t>
         </is>
       </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>3/11</t>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>75.3</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,14 +2017,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>75.3</t>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>75.3</t>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3379,24 +3379,24 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3488,32 +3488,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3521,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,37 +3549,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3613,12 +3617,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -3640,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3722,32 +3726,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3755,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3779,17 +3787,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3799,17 +3807,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3837,32 +3845,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -3870,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3906,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3914,17 +3926,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3952,32 +3964,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3985,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4025,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4029,17 +4045,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4067,32 +4083,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4100,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4124,37 +4144,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4182,32 +4202,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4215,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4239,17 +4263,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4259,17 +4283,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4445,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4494,12 +4518,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4614,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4719,17 +4743,477 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>8/11</t>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3986,12 +3986,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4202,36 +4202,32 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4239,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,17 +4259,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4283,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4321,32 +4317,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,17 +4378,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4398,17 +4398,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4436,32 +4436,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4469,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4493,17 +4497,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4513,17 +4517,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4551,32 +4555,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4584,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4608,32 +4616,32 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4666,32 +4674,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4699,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4723,17 +4735,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4743,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4868,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4978,12 +4990,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5159,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5203,17 +5215,477 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>7/11</t>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC44"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,14 +2612,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,17 +4398,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4577,12 +4577,12 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,14 +4750,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4793,32 +4793,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4826,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4850,17 +4854,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4870,12 +4874,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4908,32 +4912,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4941,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4965,17 +4973,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4985,12 +4993,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5023,32 +5031,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5056,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,37 +5092,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5138,32 +5150,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5171,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,17 +5211,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5215,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5340,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5516,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5631,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5675,17 +5691,477 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB44" s="2" t="inlineStr">
-        <is>
-          <t>75.3</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr">
-        <is>
-          <t>11/11</t>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,14 +4159,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,14 +4988,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5041,24 +5041,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5160,24 +5160,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5302,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,17 +5330,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5346,12 +5350,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5384,32 +5388,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5417,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5441,37 +5449,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5499,32 +5507,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5532,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5556,37 +5568,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5762,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,7 +5813,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5816,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5926,12 +5938,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5992,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6107,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6151,17 +6163,477 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
-        <is>
-          <t>71.3</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>4/11</t>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>70.3</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5626,32 +5626,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5659,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,17 +5687,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5703,12 +5707,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5741,32 +5745,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5774,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,17 +5806,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5818,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6004,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6119,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6234,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6349,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6464,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6518,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6623,17 +6631,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,17 +2612,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,17 +3207,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,14 +3326,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,14 +4393,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,17 +4750,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,14 +5226,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,17 +5702,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5864,32 +5864,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5897,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,37 +5925,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5979,32 +5983,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6012,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6036,32 +6044,32 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6094,32 +6102,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6127,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6151,17 +6163,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6171,12 +6183,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6209,32 +6221,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6242,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6266,37 +6282,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,7 +6422,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6472,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6587,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6641,7 +6657,582 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
           <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>71.6</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>70.8</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,17 +3207,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,14 +4159,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,14 +4988,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,17 +5583,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,17 +5702,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5993,24 +5993,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6064,17 +6064,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6124,12 +6124,12 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6340,32 +6340,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6373,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6397,32 +6401,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6455,32 +6459,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6488,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,29 +6520,29 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -6542,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6570,32 +6578,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6603,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,17 +6639,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6647,17 +6659,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6685,32 +6697,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6718,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,32 +6758,32 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6800,32 +6816,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6833,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6857,17 +6877,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6877,17 +6897,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6987,7 +7007,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7002,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7178,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7236,6 +7256,696 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>70.3</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>71.6</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,17 +2612,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,17 +3802,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,17 +4750,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6588,24 +6588,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6707,24 +6707,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,17 +6892,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6935,32 +6935,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6968,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6992,17 +6996,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -7012,12 +7016,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7050,32 +7054,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7083,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7107,37 +7115,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7165,32 +7173,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7198,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7222,17 +7234,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7242,17 +7254,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7280,32 +7292,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7313,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7337,32 +7353,32 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7428,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7482,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7658,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7707,7 +7723,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7773,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7888,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7932,17 +7948,592 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>69.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
         </is>
       </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>6/11</t>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,17 +2374,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,17 +3326,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,17 +3683,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,14 +4159,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,22 +4274,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,17 +4393,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,17 +4512,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,14 +4988,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,17 +5226,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,22 +6178,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,22 +6416,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,14 +6535,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,22 +6654,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,17 +7011,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7183,24 +7183,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7302,24 +7302,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -7411,32 +7411,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7444,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,29 +7472,29 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -7498,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7526,32 +7530,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7559,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,37 +7591,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -7641,32 +7649,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7674,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7698,17 +7710,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7718,12 +7730,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7756,32 +7768,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7789,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,37 +7829,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7871,32 +7887,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7904,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7928,32 +7948,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7986,32 +8006,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8019,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8043,37 +8067,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8216,32 +8240,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8249,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8273,32 +8301,32 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8364,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8403,7 +8431,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8413,12 +8441,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -8426,22 +8454,22 @@
       <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8474,12 +8502,12 @@
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8493,47 +8521,852 @@
       <c r="T68" s="2" t="inlineStr"/>
       <c r="U68" s="2" t="inlineStr">
         <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
           <t>18:15</t>
         </is>
       </c>
-      <c r="V68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W68" s="2" t="inlineStr">
+      <c r="W69" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X68" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y68" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z68" s="2" t="inlineStr">
+      <c r="Z69" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
+      <c r="AA69" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
+      <c r="AB69" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
         </is>
       </c>
-      <c r="AC68" s="2" t="inlineStr">
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
         <is>
           <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>69.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,22 +6059,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,22 +6416,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,22 +6892,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7135,17 +7135,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,22 +7606,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7897,24 +7897,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8125,32 +8125,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8158,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8182,17 +8186,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8202,17 +8206,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -8250,24 +8254,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8277,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8326,7 +8330,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8359,32 +8363,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8392,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8416,17 +8424,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8436,17 +8444,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8474,32 +8482,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8507,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8531,37 +8543,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -8589,32 +8601,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8622,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8646,37 +8662,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8852,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8891,7 +8907,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8906,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9021,7 +9037,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9131,7 +9147,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9197,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9246,7 +9262,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9312,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9356,17 +9372,362 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>74.1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
           <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC78"/>
+  <dimension ref="A1:AC79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7849,17 +7849,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8720,32 +8720,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8753,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8777,17 +8781,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8797,17 +8801,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8983,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9098,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9137,7 +9141,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9213,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9328,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9443,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9558,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9673,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9731,6 +9735,121 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC79"/>
+  <dimension ref="A1:AC81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,17 +3802,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6064,17 +6064,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6659,17 +6659,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6897,17 +6897,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8087,17 +8087,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8439,17 +8439,17 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8682,17 +8682,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -8730,24 +8730,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8839,32 +8839,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8872,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8896,17 +8900,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8916,12 +8920,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8954,32 +8958,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8987,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9011,17 +9019,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9031,17 +9039,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -9069,32 +9077,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9102,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,17 +9138,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9146,12 +9158,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9184,32 +9196,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9217,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9241,17 +9257,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9261,12 +9277,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9299,32 +9315,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9332,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9356,32 +9376,32 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9414,32 +9434,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9447,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9471,17 +9495,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9491,17 +9515,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9601,7 +9625,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9677,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9721,12 +9745,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9792,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9836,17 +9860,247 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>73.3</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr">
-        <is>
-          <t>6/11</t>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>70.8</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>70.2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-182路.xlsx
+++ b/data/export/2026-09-26-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4164,17 +4164,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,17 +4398,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7968,17 +7968,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8920,17 +8920,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9158,17 +9158,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -9218,12 +9218,12 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9337,12 +9337,12 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9553,32 +9553,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9586,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9610,17 +9614,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9630,12 +9634,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9668,32 +9672,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9701,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9725,17 +9733,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9745,17 +9753,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9783,32 +9791,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9816,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9840,17 +9852,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9860,17 +9872,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -9931,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10046,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10090,12 +10102,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
